--- a/data/trans_orig/P0901-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24627</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16220</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30151</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52154</t>
+          <t>53687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469437</t>
+          <t>467209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484730</t>
+          <t>485114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>431758</t>
+          <t>432390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>451269</t>
+          <t>451353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>909399</t>
+          <t>907866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>931402</t>
+          <t>932709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33811</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>38248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65017</t>
+          <t>66212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57725</t>
+          <t>57348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92873</t>
+          <t>93116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701678</t>
+          <t>702907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>721063</t>
+          <t>721945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>560477</t>
+          <t>559282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587916</t>
+          <t>587246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268109</t>
+          <t>1267866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1303257</t>
+          <t>1303634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>21579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43523</t>
+          <t>42560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>49195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>79875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77378</t>
+          <t>75952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114631</t>
+          <t>115973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>595145</t>
+          <t>596108</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617128</t>
+          <t>617089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609727</t>
+          <t>609869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>640434</t>
+          <t>640549</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1213781</t>
+          <t>1212439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1251034</t>
+          <t>1252460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50704</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58504</t>
+          <t>57852</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90661</t>
+          <t>88938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93153</t>
+          <t>92884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132461</t>
+          <t>131093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>468443</t>
+          <t>468758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>493184</t>
+          <t>492571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424981</t>
+          <t>426704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457138</t>
+          <t>457790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>902328</t>
+          <t>903696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>941636</t>
+          <t>941905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>47234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77163</t>
+          <t>74947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58679</t>
+          <t>58293</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89304</t>
+          <t>90253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115165</t>
+          <t>111878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156733</t>
+          <t>154987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309547</t>
+          <t>311763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338870</t>
+          <t>339476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314682</t>
+          <t>313733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>345307</t>
+          <t>345693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>633963</t>
+          <t>635709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>675531</t>
+          <t>678818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41261</t>
+          <t>41639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68064</t>
+          <t>66903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99142</t>
+          <t>99781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>133140</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>147883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191527</t>
+          <t>190885</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224519</t>
+          <t>225680</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251322</t>
+          <t>250944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210780</t>
+          <t>209794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243792</t>
+          <t>243153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>443990</t>
+          <t>444632</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>486874</t>
+          <t>487634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62060</t>
+          <t>63161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89203</t>
+          <t>89831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132076</t>
+          <t>130501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170323</t>
+          <t>169375</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>202481</t>
+          <t>204419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>253249</t>
+          <t>251299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>120680</t>
+          <t>120052</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147823</t>
+          <t>146722</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>163585</t>
+          <t>164533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>201832</t>
+          <t>203407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>290542</t>
+          <t>292492</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>341310</t>
+          <t>339372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>264385</t>
+          <t>264894</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>331126</t>
+          <t>336158</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>507095</t>
+          <t>510656</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>596362</t>
+          <t>594358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>795998</t>
+          <t>795588</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>909314</t>
+          <t>900460</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2945417</t>
+          <t>2940385</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3012158</t>
+          <t>3011649</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2782835</t>
+          <t>2784839</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2872102</t>
+          <t>2868541</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5746427</t>
+          <t>5755281</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5859743</t>
+          <t>5860153</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>28674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31108</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53552</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426475</t>
+          <t>425472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>443288</t>
+          <t>443056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399122</t>
+          <t>399142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417328</t>
+          <t>417698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>830824</t>
+          <t>832675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>856788</t>
+          <t>857305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>15569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35573</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42823</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40621</t>
+          <t>40212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70747</t>
+          <t>72126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>651514</t>
+          <t>651830</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>671610</t>
+          <t>671518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>567432</t>
+          <t>567529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>589157</t>
+          <t>590029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1226595</t>
+          <t>1225216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1256721</t>
+          <t>1257130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32160</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58374</t>
+          <t>57809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67518</t>
+          <t>68986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104008</t>
+          <t>104732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107939</t>
+          <t>106042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153699</t>
+          <t>153131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623489</t>
+          <t>624054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>649703</t>
+          <t>649449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>606842</t>
+          <t>606118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643332</t>
+          <t>641864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1239013</t>
+          <t>1239581</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1284773</t>
+          <t>1286670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40965</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71800</t>
+          <t>71401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79893</t>
+          <t>78681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116319</t>
+          <t>115928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127230</t>
+          <t>128307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176202</t>
+          <t>175699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>542817</t>
+          <t>543216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>573652</t>
+          <t>573462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>499880</t>
+          <t>500271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>536306</t>
+          <t>537518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1054614</t>
+          <t>1055117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1103586</t>
+          <t>1102509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>54628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86490</t>
+          <t>84920</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109333</t>
+          <t>112612</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149874</t>
+          <t>150816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>176255</t>
+          <t>174255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227690</t>
+          <t>224813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>342939</t>
+          <t>344509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>374486</t>
+          <t>374801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>297926</t>
+          <t>296984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>338467</t>
+          <t>335188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>649539</t>
+          <t>652416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>700974</t>
+          <t>702974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67245</t>
+          <t>64424</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100804</t>
+          <t>98803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>121983</t>
+          <t>122683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>161228</t>
+          <t>159259</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197382</t>
+          <t>197625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>248623</t>
+          <t>245631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208982</t>
+          <t>210983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242541</t>
+          <t>245362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192768</t>
+          <t>194737</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>232013</t>
+          <t>231313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>415159</t>
+          <t>418151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466400</t>
+          <t>466157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103550</t>
+          <t>103184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136215</t>
+          <t>136394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222230</t>
+          <t>220897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>261352</t>
+          <t>260089</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>334867</t>
+          <t>333455</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>386776</t>
+          <t>385157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113636</t>
+          <t>113457</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146301</t>
+          <t>146667</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127627</t>
+          <t>128890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>168082</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>252054</t>
+          <t>253673</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>303963</t>
+          <t>305375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>377124</t>
+          <t>373017</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>452238</t>
+          <t>456133</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>692353</t>
+          <t>690758</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>785922</t>
+          <t>793204</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1091513</t>
+          <t>1089810</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1219392</t>
+          <t>1217156</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2974541</t>
+          <t>2970646</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3049655</t>
+          <t>3053762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2772387</t>
+          <t>2765105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2865956</t>
+          <t>2867551</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5765696</t>
+          <t>5767932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5893575</t>
+          <t>5895278</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,4%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22699</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33230</t>
+          <t>32021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403015</t>
+          <t>403136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415640</t>
+          <t>415620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>373056</t>
+          <t>374822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388068</t>
+          <t>388259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>781988</t>
+          <t>783197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>800736</t>
+          <t>801919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37853</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>24085</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>49068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46516</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77717</t>
+          <t>77215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>552643</t>
+          <t>551981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>573152</t>
+          <t>572818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516631</t>
+          <t>514476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>539300</t>
+          <t>539459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1076323</t>
+          <t>1076825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1107524</t>
+          <t>1107653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41217</t>
+          <t>41046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45822</t>
+          <t>45167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75038</t>
+          <t>77194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69335</t>
+          <t>68940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108824</t>
+          <t>106270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627880</t>
+          <t>628051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>649773</t>
+          <t>649830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>586348</t>
+          <t>584192</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615564</t>
+          <t>616219</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1221659</t>
+          <t>1224213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1261148</t>
+          <t>1261543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51325</t>
+          <t>50944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84533</t>
+          <t>85207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71255</t>
+          <t>70602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107371</t>
+          <t>104202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130985</t>
+          <t>132141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177452</t>
+          <t>180721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>561515</t>
+          <t>560841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>594723</t>
+          <t>595104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>541706</t>
+          <t>544875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>577822</t>
+          <t>578475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1117673</t>
+          <t>1114404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1164140</t>
+          <t>1162984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>48556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82654</t>
+          <t>81761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102179</t>
+          <t>101990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143683</t>
+          <t>140783</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158817</t>
+          <t>159093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214113</t>
+          <t>212031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>395264</t>
+          <t>396157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427655</t>
+          <t>429362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>353166</t>
+          <t>356066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394670</t>
+          <t>394859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>760654</t>
+          <t>762736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>815950</t>
+          <t>815674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50563</t>
+          <t>50303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79312</t>
+          <t>79940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125804</t>
+          <t>123050</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166010</t>
+          <t>163785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184075</t>
+          <t>181906</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233702</t>
+          <t>232334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255018</t>
+          <t>254390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283767</t>
+          <t>284027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211752</t>
+          <t>213977</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251958</t>
+          <t>254712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>478390</t>
+          <t>479758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528017</t>
+          <t>530186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83659</t>
+          <t>84233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112650</t>
+          <t>111517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208962</t>
+          <t>210501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252980</t>
+          <t>254587</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>302304</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>358668</t>
+          <t>357725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>144348</t>
+          <t>145481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>173339</t>
+          <t>172765</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147189</t>
+          <t>145582</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>191207</t>
+          <t>189668</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>298499</t>
+          <t>299442</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>353154</t>
+          <t>354863</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322135</t>
+          <t>323257</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>392663</t>
+          <t>393536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>641640</t>
+          <t>639480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>740543</t>
+          <t>736634</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>981712</t>
+          <t>987151</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1107494</t>
+          <t>1107887</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3001687</t>
+          <t>3000814</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3072215</t>
+          <t>3071093</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2803999</t>
+          <t>2807908</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2902902</t>
+          <t>2905062</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5831398</t>
+          <t>5831005</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5957180</t>
+          <t>5951741</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28403</t>
+          <t>24368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>39111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374962</t>
+          <t>374880</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398105</t>
+          <t>398002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284797</t>
+          <t>288832</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308172</t>
+          <t>308850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673717</t>
+          <t>674076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>703783</t>
+          <t>703277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>19856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>47705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37029</t>
+          <t>36588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73316</t>
+          <t>76006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377825</t>
+          <t>375842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403860</t>
+          <t>403691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473935</t>
+          <t>474376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498951</t>
+          <t>496658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>861195</t>
+          <t>858505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>895711</t>
+          <t>895343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>31912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58538</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46698</t>
+          <t>46728</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70204</t>
+          <t>70545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84574</t>
+          <t>85417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123071</t>
+          <t>120196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477800</t>
+          <t>477373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504706</t>
+          <t>504426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>472264</t>
+          <t>471923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>495770</t>
+          <t>495740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>955735</t>
+          <t>958610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>994232</t>
+          <t>993389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37627</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130443</t>
+          <t>128002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95062</t>
+          <t>94415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134881</t>
+          <t>133066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113971</t>
+          <t>125135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>245969</t>
+          <t>251270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756253</t>
+          <t>758694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849069</t>
+          <t>849685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>577367</t>
+          <t>579182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>617186</t>
+          <t>617833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1352975</t>
+          <t>1347674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1484973</t>
+          <t>1473809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96543</t>
+          <t>96853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133842</t>
+          <t>135026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118991</t>
+          <t>119197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149198</t>
+          <t>148921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225038</t>
+          <t>224126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273789</t>
+          <t>274964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427392</t>
+          <t>426208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>464691</t>
+          <t>464381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>398707</t>
+          <t>398984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428914</t>
+          <t>428708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835350</t>
+          <t>834175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>884101</t>
+          <t>885013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53248</t>
+          <t>54889</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76954</t>
+          <t>78077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>51643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186301</t>
+          <t>186344</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96404</t>
+          <t>96038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>241358</t>
+          <t>240906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290641</t>
+          <t>289518</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314347</t>
+          <t>312706</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>422067</t>
+          <t>422024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>559549</t>
+          <t>556725</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>734605</t>
+          <t>735057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>879559</t>
+          <t>879925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>87044</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113174</t>
+          <t>112568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223349</t>
+          <t>222616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>253383</t>
+          <t>252260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>317401</t>
+          <t>318604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>356389</t>
+          <t>355923</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169082</t>
+          <t>169688</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196050</t>
+          <t>195212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>172014</t>
+          <t>173137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>202048</t>
+          <t>202781</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>351265</t>
+          <t>351731</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>390253</t>
+          <t>389050</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>356462</t>
+          <t>344105</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>503192</t>
+          <t>500524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>559095</t>
+          <t>566674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>760672</t>
+          <t>762632</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1003297</t>
+          <t>990136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1231605</t>
+          <t>1238738</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2954461</t>
+          <t>2957129</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3101191</t>
+          <t>3113548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2899878</t>
+          <t>2897918</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3101455</t>
+          <t>3093876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5886597</t>
+          <t>5879464</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6114905</t>
+          <t>6128066</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0901-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>24071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>15829</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35099</t>
+          <t>34289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28844</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53687</t>
+          <t>55328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467209</t>
+          <t>469993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>485114</t>
+          <t>485219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432390</t>
+          <t>433200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>451353</t>
+          <t>451660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>907866</t>
+          <t>906225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>932709</t>
+          <t>932207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32582</t>
+          <t>33469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38248</t>
+          <t>38524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66212</t>
+          <t>65954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57348</t>
+          <t>58664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93116</t>
+          <t>94331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>702907</t>
+          <t>702020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>721945</t>
+          <t>721195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559282</t>
+          <t>559540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587246</t>
+          <t>586970</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267866</t>
+          <t>1266651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1303634</t>
+          <t>1302318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49195</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79875</t>
+          <t>79798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75952</t>
+          <t>75667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115973</t>
+          <t>114098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596108</t>
+          <t>594588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617089</t>
+          <t>617298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609869</t>
+          <t>609946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>640549</t>
+          <t>640268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1212439</t>
+          <t>1214314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1252460</t>
+          <t>1252745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50389</t>
+          <t>50482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57852</t>
+          <t>57844</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88938</t>
+          <t>89587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92884</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131093</t>
+          <t>131588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>468758</t>
+          <t>468665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492571</t>
+          <t>491931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426704</t>
+          <t>426055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457790</t>
+          <t>457798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>903696</t>
+          <t>903201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>941905</t>
+          <t>943376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47234</t>
+          <t>47640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74947</t>
+          <t>75352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58293</t>
+          <t>58612</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90253</t>
+          <t>88894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111878</t>
+          <t>114659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154987</t>
+          <t>154425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>311763</t>
+          <t>311358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339476</t>
+          <t>339070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>313733</t>
+          <t>315092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>345693</t>
+          <t>345374</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>635709</t>
+          <t>636271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>678818</t>
+          <t>676037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41639</t>
+          <t>41943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66903</t>
+          <t>68265</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99781</t>
+          <t>99249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133140</t>
+          <t>134671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147883</t>
+          <t>148284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>190885</t>
+          <t>190710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225680</t>
+          <t>224318</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250944</t>
+          <t>250640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209794</t>
+          <t>208263</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243153</t>
+          <t>243685</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>444632</t>
+          <t>444807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>487634</t>
+          <t>487233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63161</t>
+          <t>63181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89831</t>
+          <t>89251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130501</t>
+          <t>131350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169375</t>
+          <t>169061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>204419</t>
+          <t>205240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251299</t>
+          <t>251697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>120052</t>
+          <t>120632</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146722</t>
+          <t>146702</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164533</t>
+          <t>164847</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203407</t>
+          <t>202558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>292492</t>
+          <t>292094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>339372</t>
+          <t>338551</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,26%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>264894</t>
+          <t>266224</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>336158</t>
+          <t>332220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>510656</t>
+          <t>509670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>594358</t>
+          <t>596973</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>795588</t>
+          <t>795572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>900460</t>
+          <t>901563</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2940385</t>
+          <t>2944323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3011649</t>
+          <t>3010319</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2784839</t>
+          <t>2782224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2868541</t>
+          <t>2869527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5755281</t>
+          <t>5754178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5860153</t>
+          <t>5860169</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28674</t>
+          <t>29654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>27723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51701</t>
+          <t>53082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>425472</t>
+          <t>424492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>443056</t>
+          <t>442132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399142</t>
+          <t>399973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417698</t>
+          <t>417433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>832675</t>
+          <t>831294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>857305</t>
+          <t>856653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35257</t>
+          <t>35442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42726</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40212</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72126</t>
+          <t>70664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>651830</t>
+          <t>651645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>671518</t>
+          <t>670825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>567529</t>
+          <t>567091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>590029</t>
+          <t>590251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1225216</t>
+          <t>1226678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1257130</t>
+          <t>1256063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57809</t>
+          <t>60852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68986</t>
+          <t>65987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104732</t>
+          <t>103677</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106042</t>
+          <t>107384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153131</t>
+          <t>151286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>621011</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>649449</t>
+          <t>648823</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>606118</t>
+          <t>607173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641864</t>
+          <t>644863</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1239581</t>
+          <t>1241426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1286670</t>
+          <t>1285328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>41603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71401</t>
+          <t>70553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78681</t>
+          <t>78037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115928</t>
+          <t>116762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128307</t>
+          <t>128261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175699</t>
+          <t>173873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543216</t>
+          <t>544064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>573462</t>
+          <t>573014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>500271</t>
+          <t>499437</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>537518</t>
+          <t>538162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1055117</t>
+          <t>1056943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1102509</t>
+          <t>1102555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54628</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84920</t>
+          <t>86229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112612</t>
+          <t>112408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150816</t>
+          <t>151639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>174255</t>
+          <t>176672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224813</t>
+          <t>227638</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>344509</t>
+          <t>343200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>374801</t>
+          <t>373305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>296984</t>
+          <t>296161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>335188</t>
+          <t>335392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>652416</t>
+          <t>649591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702974</t>
+          <t>700557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64424</t>
+          <t>65433</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98803</t>
+          <t>99952</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122683</t>
+          <t>120501</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159259</t>
+          <t>158444</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197625</t>
+          <t>198873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>245631</t>
+          <t>247327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210983</t>
+          <t>209834</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245362</t>
+          <t>244353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>194737</t>
+          <t>195552</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231313</t>
+          <t>233495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>418151</t>
+          <t>416455</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466157</t>
+          <t>464909</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103184</t>
+          <t>103491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136394</t>
+          <t>136589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>220897</t>
+          <t>220094</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>260089</t>
+          <t>261782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333455</t>
+          <t>333324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>385157</t>
+          <t>388859</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,87%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113457</t>
+          <t>113262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146667</t>
+          <t>146360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128890</t>
+          <t>127197</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>168082</t>
+          <t>168885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>253673</t>
+          <t>249971</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>305375</t>
+          <t>305506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>373017</t>
+          <t>372736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>456133</t>
+          <t>457774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>690758</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>793204</t>
+          <t>793882</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1089810</t>
+          <t>1091529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1217156</t>
+          <t>1218293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2970646</t>
+          <t>2969005</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3053762</t>
+          <t>3054043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2765105</t>
+          <t>2764427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2867551</t>
+          <t>2864106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5767932</t>
+          <t>5766795</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5895278</t>
+          <t>5893559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32021</t>
+          <t>32258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403136</t>
+          <t>402704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415620</t>
+          <t>415541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>374822</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388259</t>
+          <t>388408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>783197</t>
+          <t>782960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>801919</t>
+          <t>801504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24085</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49068</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77215</t>
+          <t>77829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>551981</t>
+          <t>552308</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>572818</t>
+          <t>573115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514476</t>
+          <t>517282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>539459</t>
+          <t>539755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1076825</t>
+          <t>1076211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1107653</t>
+          <t>1108368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41046</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45167</t>
+          <t>45310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77194</t>
+          <t>75275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68940</t>
+          <t>70438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106270</t>
+          <t>109519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628051</t>
+          <t>629641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>649830</t>
+          <t>649636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>584192</t>
+          <t>586111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>616219</t>
+          <t>616076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1224213</t>
+          <t>1220964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1261543</t>
+          <t>1260045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50944</t>
+          <t>53261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85207</t>
+          <t>84653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70602</t>
+          <t>70325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104202</t>
+          <t>105391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132141</t>
+          <t>130378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180721</t>
+          <t>181433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>560841</t>
+          <t>561395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>595104</t>
+          <t>592787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>544875</t>
+          <t>543686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578475</t>
+          <t>578752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1114404</t>
+          <t>1113692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1162984</t>
+          <t>1164747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48556</t>
+          <t>47692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81761</t>
+          <t>80117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101990</t>
+          <t>101123</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>140783</t>
+          <t>139935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159093</t>
+          <t>158969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212031</t>
+          <t>210051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396157</t>
+          <t>397801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>429362</t>
+          <t>430226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>356066</t>
+          <t>356914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394859</t>
+          <t>395726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>762736</t>
+          <t>764716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>815674</t>
+          <t>815798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50303</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79940</t>
+          <t>77851</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123050</t>
+          <t>123910</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>163785</t>
+          <t>163155</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181906</t>
+          <t>183996</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232334</t>
+          <t>234724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254390</t>
+          <t>256479</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284027</t>
+          <t>283985</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213977</t>
+          <t>214607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254712</t>
+          <t>253852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479758</t>
+          <t>477368</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>530186</t>
+          <t>528096</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84233</t>
+          <t>84328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111517</t>
+          <t>112461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210501</t>
+          <t>208992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254587</t>
+          <t>253186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>302304</t>
+          <t>301262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>357725</t>
+          <t>359040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>145481</t>
+          <t>144537</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>172765</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145582</t>
+          <t>146983</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>189668</t>
+          <t>191177</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>299442</t>
+          <t>298127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354863</t>
+          <t>355905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>323257</t>
+          <t>319716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>393536</t>
+          <t>394196</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>639480</t>
+          <t>635291</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>736634</t>
+          <t>741820</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>987151</t>
+          <t>976514</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1107887</t>
+          <t>1106741</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3000814</t>
+          <t>3000154</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3071093</t>
+          <t>3074634</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2807908</t>
+          <t>2802722</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2905062</t>
+          <t>2909251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5831005</t>
+          <t>5832151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5951741</t>
+          <t>5962378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25107</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24368</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>43729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>391599</t>
+          <t>400095</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374880</t>
+          <t>385575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398002</t>
+          <t>406312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>344777</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288832</t>
+          <t>327025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308850</t>
+          <t>354327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>692559</t>
+          <t>744872</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674076</t>
+          <t>726576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>703277</t>
+          <t>757641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>20343</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47705</t>
+          <t>47926</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54542</t>
+          <t>58837</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76006</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>393077</t>
+          <t>444317</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375842</t>
+          <t>428964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403691</t>
+          <t>456547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>486892</t>
+          <t>474240</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474376</t>
+          <t>461734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496658</t>
+          <t>483140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>879969</t>
+          <t>918557</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>858505</t>
+          <t>899363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>895343</t>
+          <t>934304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>45547</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>61494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,67 +10386,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>64982</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46728</t>
+          <t>52264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70545</t>
+          <t>78715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>110529</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>91813</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>132031</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>10,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>101492</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>85417</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>120196</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>492449</t>
+          <t>575290</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477373</t>
+          <t>559343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504426</t>
+          <t>588043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,67 +10499,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>484865</t>
+          <t>557157</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>471923</t>
+          <t>543424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>495740</t>
+          <t>569875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>89,56%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>87,35%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>91,6%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1132447</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1110945</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1151163</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>91,11%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>89,38%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>91,39%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>977314</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>958610</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>993389</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>88,86%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86878</t>
+          <t>94984</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>76909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128002</t>
+          <t>116390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,27 +10729,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>112849</t>
+          <t>119594</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94415</t>
+          <t>103715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133066</t>
+          <t>137560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>199726</t>
+          <t>214577</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125135</t>
+          <t>189741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251270</t>
+          <t>240568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>799818</t>
+          <t>604529</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>758694</t>
+          <t>583123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849685</t>
+          <t>622604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,22 +10842,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>599399</t>
+          <t>616649</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>579182</t>
+          <t>598683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>617833</t>
+          <t>632528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1399218</t>
+          <t>1221179</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1347674</t>
+          <t>1195188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1473809</t>
+          <t>1246015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>86,78%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886696</t>
+          <t>699513</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886696</t>
+          <t>699513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886696</t>
+          <t>699513</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712248</t>
+          <t>736243</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712248</t>
+          <t>736243</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712248</t>
+          <t>736243</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598944</t>
+          <t>1435756</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598944</t>
+          <t>1435756</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598944</t>
+          <t>1435756</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>114630</t>
+          <t>120550</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96853</t>
+          <t>102643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135026</t>
+          <t>140285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>134057</t>
+          <t>152034</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119197</t>
+          <t>136673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148921</t>
+          <t>167815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>248687</t>
+          <t>272585</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224126</t>
+          <t>246423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>274964</t>
+          <t>299435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>446604</t>
+          <t>488796</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426208</t>
+          <t>469061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>464381</t>
+          <t>506703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>413848</t>
+          <t>456821</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>398984</t>
+          <t>441040</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428708</t>
+          <t>472182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>860452</t>
+          <t>945617</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>834175</t>
+          <t>918767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>885013</t>
+          <t>971779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65149</t>
+          <t>70172</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54889</t>
+          <t>57886</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78077</t>
+          <t>84962</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>119537</t>
+          <t>131175</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51643</t>
+          <t>117061</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186344</t>
+          <t>145352</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>184686</t>
+          <t>201347</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96038</t>
+          <t>182475</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240906</t>
+          <t>220588</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>302446</t>
+          <t>336321</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289518</t>
+          <t>321531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312706</t>
+          <t>348607</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>488831</t>
+          <t>307991</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>422024</t>
+          <t>293814</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>556725</t>
+          <t>322105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>791277</t>
+          <t>644313</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>735057</t>
+          <t>625072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>879925</t>
+          <t>663185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>99316</t>
+          <t>109480</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87044</t>
+          <t>95185</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112568</t>
+          <t>124856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>237673</t>
+          <t>262248</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222616</t>
+          <t>247444</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252260</t>
+          <t>279219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>336990</t>
+          <t>371728</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>318604</t>
+          <t>350094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>355923</t>
+          <t>393483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>182940</t>
+          <t>200226</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169688</t>
+          <t>184850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195212</t>
+          <t>214521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>187724</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>173137</t>
+          <t>184924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>202781</t>
+          <t>216699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>370664</t>
+          <t>402121</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>351731</t>
+          <t>380366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>389050</t>
+          <t>423755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,76%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282256</t>
+          <t>309706</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282256</t>
+          <t>309706</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282256</t>
+          <t>309706</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425397</t>
+          <t>464143</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425397</t>
+          <t>464143</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425397</t>
+          <t>464143</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707654</t>
+          <t>773849</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707654</t>
+          <t>773849</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707654</t>
+          <t>773849</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>448719</t>
+          <t>481003</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>438177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>500524</t>
+          <t>522614</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>698033</t>
+          <t>774032</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>566674</t>
+          <t>734684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>762632</t>
+          <t>817138</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1146752</t>
+          <t>1255035</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>990136</t>
+          <t>1194796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1238738</t>
+          <t>1324056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3008934</t>
+          <t>3049576</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2957129</t>
+          <t>3007965</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3113548</t>
+          <t>3092402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2962517</t>
+          <t>2959531</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2897918</t>
+          <t>2916425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3093876</t>
+          <t>2998879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5971450</t>
+          <t>6009107</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5879464</t>
+          <t>5940086</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6128066</t>
+          <t>6069346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
